--- a/Result/profitability/4205.xlsx
+++ b/Result/profitability/4205.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.36</v>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>0.9762500000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>38.94875</v>
+        <v>38.5375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.4</v>
       </c>
       <c r="M3" t="n">
-        <v>0.90625</v>
+        <v>0.85625</v>
       </c>
       <c r="N3" t="n">
-        <v>38.6775</v>
+        <v>38.155</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.63</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.8075</v>
       </c>
       <c r="N4" t="n">
-        <v>38.68875</v>
+        <v>38.50875000000001</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.47</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7462500000000001</v>
+        <v>0.73</v>
       </c>
       <c r="N5" t="n">
-        <v>38.55</v>
+        <v>38.06</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.63</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6887500000000001</v>
+        <v>0.6875</v>
       </c>
       <c r="N6" t="n">
-        <v>38.42375</v>
+        <v>37.98375</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.6</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6425</v>
+        <v>0.6174999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>38.63</v>
+        <v>38.30375</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.62</v>
       </c>
       <c r="M8" t="n">
-        <v>0.575</v>
+        <v>0.58375</v>
       </c>
       <c r="N8" t="n">
-        <v>39.02625</v>
+        <v>39.135</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>4205</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>492</v>
+      </c>
+      <c r="D75" t="n">
+        <v>309</v>
+      </c>
+      <c r="E75" t="n">
+        <v>183</v>
+      </c>
+      <c r="F75" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="G75" t="n">
+        <v>104</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>21.16%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>7</v>
+      </c>
+      <c r="J75" t="n">
+        <v>111</v>
+      </c>
+      <c r="K75" t="n">
+        <v>94</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.075</v>
+      </c>
+      <c r="N75" t="n">
+        <v>39.46125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.06999999999999995</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.0786516853932584</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.8700000000000045</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.0239471511147813</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.1300000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.1192660550458716</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-3.919999999999995</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.09533073929961078</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
